--- a/Prowizje_AB.xlsx
+++ b/Prowizje_AB.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://studmsugedupl-my.sharepoint.com/personal/a_mazur_177_studms_ug_edu_pl/Documents/Dokumenty/Praca/P&amp;L/PiL_excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="175" documentId="8_{669BC07B-79E8-4062-8387-50661E039DB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ED05AA55-4888-4EE3-8676-5E8CDF40DA14}"/>
+  <xr:revisionPtr revIDLastSave="181" documentId="8_{669BC07B-79E8-4062-8387-50661E039DB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B481D4FD-3E53-421F-8942-ED34AB57E161}"/>
   <bookViews>
-    <workbookView xWindow="20655" yWindow="0" windowWidth="17745" windowHeight="21600" xr2:uid="{CE3FF967-4599-4E35-AD71-6CCC415A1E0C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{CE3FF967-4599-4E35-AD71-6CCC415A1E0C}"/>
   </bookViews>
   <sheets>
     <sheet name="provision(Provisions)" sheetId="1" r:id="rId1"/>
@@ -30,28 +30,6 @@
     </ext>
   </extLst>
 </workbook>
-</file>
-
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1665,7 +1643,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FE84C79-BF9B-4095-8C66-38595DEB2045}">
-  <dimension ref="A1:I713"/>
+  <dimension ref="A1:H713"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.85546875" bestFit="1" customWidth="1"/>
@@ -9020,7 +8998,7 @@
         <v>45658</v>
       </c>
       <c r="D283" s="1">
-        <v>45808</v>
+        <v>46022</v>
       </c>
       <c r="E283" s="2">
         <v>0</v>
@@ -9043,10 +9021,10 @@
         <v>1125</v>
       </c>
       <c r="C284" s="1">
-        <v>45809</v>
+        <v>46023</v>
       </c>
       <c r="D284" s="1">
-        <v>45808</v>
+        <v>46387</v>
       </c>
       <c r="E284" s="2">
         <v>0</v>
@@ -19981,7 +19959,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="705" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A705" t="s">
         <v>13</v>
       </c>
@@ -20007,7 +19985,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="706" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A706" t="s">
         <v>13</v>
       </c>
@@ -20033,7 +20011,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="707" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A707" t="s">
         <v>13</v>
       </c>
@@ -20059,7 +20037,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="708" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A708" t="s">
         <v>12</v>
       </c>
@@ -20085,7 +20063,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="709" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A709" t="s">
         <v>13</v>
       </c>
@@ -20111,7 +20089,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="710" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A710" t="s">
         <v>12</v>
       </c>
@@ -20137,7 +20115,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="711" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A711" t="s">
         <v>11</v>
       </c>
@@ -20163,7 +20141,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="712" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A712" t="s">
         <v>7</v>
       </c>
@@ -20189,7 +20167,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="713" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A713" t="s">
         <v>7</v>
       </c>
@@ -20213,10 +20191,6 @@
       </c>
       <c r="H713" t="s">
         <v>6</v>
-      </c>
-      <c r="I713" cm="1">
-        <f t="array" aca="1" ref="I713" ca="1">H1:I713</f>
-        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -20226,11 +20200,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="ee04e7f4-486a-44ee-b1bb-84cf7d29fc26" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -20422,26 +20397,17 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="ee04e7f4-486a-44ee-b1bb-84cf7d29fc26" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F9CC30DC-1D82-47A1-87AC-B6B5CB82B4B2}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B11B2F7C-D452-47EB-9045-D6259F1CDB17}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="ee04e7f4-486a-44ee-b1bb-84cf7d29fc26"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -20465,9 +20431,17 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B11B2F7C-D452-47EB-9045-D6259F1CDB17}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F9CC30DC-1D82-47A1-87AC-B6B5CB82B4B2}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="ee04e7f4-486a-44ee-b1bb-84cf7d29fc26"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Prowizje_AB.xlsx
+++ b/Prowizje_AB.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://studmsugedupl-my.sharepoint.com/personal/a_mazur_177_studms_ug_edu_pl/Documents/Dokumenty/Praca/P&amp;L/PiL_excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="175" documentId="8_{669BC07B-79E8-4062-8387-50661E039DB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ED05AA55-4888-4EE3-8676-5E8CDF40DA14}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{3CCC7237-2D29-4BCB-9DF1-22CA6AB96E08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20655" yWindow="0" windowWidth="17745" windowHeight="21600" xr2:uid="{CE3FF967-4599-4E35-AD71-6CCC415A1E0C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{CE3FF967-4599-4E35-AD71-6CCC415A1E0C}"/>
   </bookViews>
   <sheets>
     <sheet name="provision(Provisions)" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" calcCompleted="0"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1344,10 +1344,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Motyw pakietu Office">
   <a:themeElements>
@@ -20226,11 +20222,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="ee04e7f4-486a-44ee-b1bb-84cf7d29fc26" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -20422,26 +20419,17 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="ee04e7f4-486a-44ee-b1bb-84cf7d29fc26" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F9CC30DC-1D82-47A1-87AC-B6B5CB82B4B2}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B11B2F7C-D452-47EB-9045-D6259F1CDB17}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="ee04e7f4-486a-44ee-b1bb-84cf7d29fc26"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -20465,9 +20453,17 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B11B2F7C-D452-47EB-9045-D6259F1CDB17}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F9CC30DC-1D82-47A1-87AC-B6B5CB82B4B2}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="ee04e7f4-486a-44ee-b1bb-84cf7d29fc26"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Prowizje_AB.xlsx
+++ b/Prowizje_AB.xlsx
@@ -10,12 +10,12 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="14_{3CCC7237-2D29-4BCB-9DF1-22CA6AB96E08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{CE3FF967-4599-4E35-AD71-6CCC415A1E0C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{CE3FF967-4599-4E35-AD71-6CCC415A1E0C}"/>
   </bookViews>
   <sheets>
     <sheet name="provision(Provisions)" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" calcCompleted="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -20222,12 +20222,11 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="ee04e7f4-486a-44ee-b1bb-84cf7d29fc26" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -20419,17 +20418,26 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="ee04e7f4-486a-44ee-b1bb-84cf7d29fc26" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B11B2F7C-D452-47EB-9045-D6259F1CDB17}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F9CC30DC-1D82-47A1-87AC-B6B5CB82B4B2}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="ee04e7f4-486a-44ee-b1bb-84cf7d29fc26"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -20453,17 +20461,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F9CC30DC-1D82-47A1-87AC-B6B5CB82B4B2}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B11B2F7C-D452-47EB-9045-D6259F1CDB17}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="ee04e7f4-486a-44ee-b1bb-84cf7d29fc26"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Prowizje_AB.xlsx
+++ b/Prowizje_AB.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://studmsugedupl-my.sharepoint.com/personal/a_mazur_177_studms_ug_edu_pl/Documents/Dokumenty/Praca/P&amp;L/PiL_excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{3CCC7237-2D29-4BCB-9DF1-22CA6AB96E08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="14_{3CCC7237-2D29-4BCB-9DF1-22CA6AB96E08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3AE48702-0D2F-4FC9-AFE2-76F043A8BED3}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{CE3FF967-4599-4E35-AD71-6CCC415A1E0C}"/>
+    <workbookView minimized="1" xWindow="24255" yWindow="2355" windowWidth="8970" windowHeight="8415" xr2:uid="{CE3FF967-4599-4E35-AD71-6CCC415A1E0C}"/>
   </bookViews>
   <sheets>
     <sheet name="provision(Provisions)" sheetId="1" r:id="rId1"/>
@@ -2588,7 +2588,7 @@
         <v>11</v>
       </c>
       <c r="B36">
-        <v>1103</v>
+        <v>103</v>
       </c>
       <c r="C36" s="1">
         <v>46023</v>

--- a/Prowizje_AB.xlsx
+++ b/Prowizje_AB.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="1" documentId="14_{3CCC7237-2D29-4BCB-9DF1-22CA6AB96E08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3AE48702-0D2F-4FC9-AFE2-76F043A8BED3}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="24255" yWindow="2355" windowWidth="8970" windowHeight="8415" xr2:uid="{CE3FF967-4599-4E35-AD71-6CCC415A1E0C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{CE3FF967-4599-4E35-AD71-6CCC415A1E0C}"/>
   </bookViews>
   <sheets>
     <sheet name="provision(Provisions)" sheetId="1" r:id="rId1"/>
@@ -20222,11 +20222,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="ee04e7f4-486a-44ee-b1bb-84cf7d29fc26" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -20418,26 +20419,17 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="ee04e7f4-486a-44ee-b1bb-84cf7d29fc26" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F9CC30DC-1D82-47A1-87AC-B6B5CB82B4B2}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B11B2F7C-D452-47EB-9045-D6259F1CDB17}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="ee04e7f4-486a-44ee-b1bb-84cf7d29fc26"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -20461,9 +20453,17 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B11B2F7C-D452-47EB-9045-D6259F1CDB17}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F9CC30DC-1D82-47A1-87AC-B6B5CB82B4B2}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="ee04e7f4-486a-44ee-b1bb-84cf7d29fc26"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>